--- a/artfynd/A 22464-2022 artfynd.xlsx
+++ b/artfynd/A 22464-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22464-2022 artfynd.xlsx
+++ b/artfynd/A 22464-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2037,6 +2037,108 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126543901</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Låddberget S, Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>453622</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6868880</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22464-2022 artfynd.xlsx
+++ b/artfynd/A 22464-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104055295</v>
+        <v>104055901</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453345.3019899689</v>
+        <v>453429</v>
       </c>
       <c r="R2" t="n">
-        <v>6868974.058034748</v>
+        <v>6868933</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,19 +773,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104055375</v>
+        <v>104055295</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453363.4146991592</v>
+        <v>453345</v>
       </c>
       <c r="R3" t="n">
-        <v>6869023.226088724</v>
+        <v>6868974</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +871,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104055503</v>
+        <v>104055322</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453415.7714877446</v>
+        <v>453287</v>
       </c>
       <c r="R4" t="n">
-        <v>6868922.735247222</v>
+        <v>6868983</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104055701</v>
+        <v>104055349</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453291.6636891001</v>
+        <v>453324</v>
       </c>
       <c r="R5" t="n">
-        <v>6869015.267513825</v>
+        <v>6869021</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,19 +1067,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104055322</v>
+        <v>104055375</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453286.9836339725</v>
+        <v>453364</v>
       </c>
       <c r="R6" t="n">
-        <v>6868983.328857425</v>
+        <v>6869023</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,19 +1165,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104055457</v>
+        <v>104055401</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453539.4762685933</v>
+        <v>453390</v>
       </c>
       <c r="R7" t="n">
-        <v>6868869.274624098</v>
+        <v>6869020</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,19 +1263,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104055349</v>
+        <v>104055457</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453323.7918913565</v>
+        <v>453539</v>
       </c>
       <c r="R8" t="n">
-        <v>6869020.945169445</v>
+        <v>6868870</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104055726</v>
+        <v>104055491</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1372,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453318.3950132527</v>
+        <v>453472</v>
       </c>
       <c r="R9" t="n">
-        <v>6869039.844171816</v>
+        <v>6868895</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,19 +1459,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104055552</v>
+        <v>104055503</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453528.422848041</v>
+        <v>453416</v>
       </c>
       <c r="R10" t="n">
-        <v>6868888.251259104</v>
+        <v>6868923</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,19 +1557,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104055526</v>
+        <v>104055512</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1733,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453312.3463396754</v>
+        <v>453381</v>
       </c>
       <c r="R11" t="n">
-        <v>6869045.574579127</v>
+        <v>6868941</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,19 +1655,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104157884</v>
+        <v>104055526</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1839,19 +1684,20 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Risbrunn, Hjd</t>
+          <t>Låddberget S, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453296.2144382891</v>
+        <v>453313</v>
       </c>
       <c r="R12" t="n">
-        <v>6869072.15060285</v>
+        <v>6869045</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,27 +1721,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,31 +1741,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104157883</v>
+        <v>104055552</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1956,19 +1782,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Risbrunn, Hjd</t>
+          <t>Låddberget S, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453592.2414648004</v>
+        <v>453528</v>
       </c>
       <c r="R13" t="n">
-        <v>6868901.97097528</v>
+        <v>6868889</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,27 +1819,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,22 +1839,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126543901</v>
+        <v>104157883</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,34 +1862,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Låddberget S, Låddberget S, Hjd</t>
+          <t>Risbrunn, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453622</v>
+        <v>453592</v>
       </c>
       <c r="R14" t="n">
-        <v>6868880</v>
+        <v>6868902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,17 +1916,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gamla ringhack på tall.</t>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,15 +1941,1003 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104157884</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risbrunn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>453296</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6869072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96977353</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Låddberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>453500</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6868954</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>96977366</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Låddberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>453429</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6868933</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96977381</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Låddberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>453476</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6868788</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104055701</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>453292</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6869016</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104055726</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>453319</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6869040</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104055747</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>453274</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6869001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126543901</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Låddberget S, Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>453622</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6868880</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96977259</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Låddberget 500m V Betlehem, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>453466</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6868931</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126544256</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Låddberget S, Låddberget S, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>453444</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6868894</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22464-2022 artfynd.xlsx
+++ b/artfynd/A 22464-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055901</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055295</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055322</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055375</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055457</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055491</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055503</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055512</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055552</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157883</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157884</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96977353</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2248,6 +2328,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96977366</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96977381</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2444,6 +2534,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055701</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055726</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104055747</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2742,6 +2847,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126543901</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96977259</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,8 +3053,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126544256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>